--- a/data/trans_dic/P16A03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A03-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,67</t>
+          <t>0,17; 1,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,02</t>
+          <t>0,23; 2,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,36</t>
+          <t>2,53; 6,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,92</t>
+          <t>1,14; 3,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,99</t>
+          <t>1,64; 5,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 6,07</t>
+          <t>0,48; 5,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,39</t>
+          <t>1,41; 3,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,38</t>
+          <t>0,89; 2,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,43</t>
+          <t>0,83; 2,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,06</t>
+          <t>0,35; 2,88</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,62</t>
+          <t>0,36; 1,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,65</t>
+          <t>0,58; 2,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,13</t>
+          <t>0,34; 2,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,05</t>
+          <t>0,04; 2,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,6</t>
+          <t>3,11; 6,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,75</t>
+          <t>3,81; 7,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,13</t>
+          <t>1,55; 4,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,1</t>
+          <t>1,25; 4,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,58</t>
+          <t>1,77; 3,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,47</t>
+          <t>2,47; 4,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,73</t>
+          <t>1,16; 2,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,83</t>
+          <t>0,84; 2,88</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,67</t>
+          <t>1,04; 3,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,63</t>
+          <t>0,27; 1,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,61</t>
+          <t>0,16; 1,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,6</t>
+          <t>0,43; 2,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,77</t>
+          <t>2,04; 4,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,7</t>
+          <t>4,18; 7,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,93</t>
+          <t>2,82; 5,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,86</t>
+          <t>1,77; 4,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,73</t>
+          <t>1,93; 3,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,36</t>
+          <t>2,42; 4,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,23</t>
+          <t>1,57; 3,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,82</t>
+          <t>1,29; 2,8</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,26</t>
+          <t>0,77; 3,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,9</t>
+          <t>0,33; 1,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,14</t>
+          <t>0,38; 2,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,86</t>
+          <t>0,56; 2,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,23</t>
+          <t>2,48; 6,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,65</t>
+          <t>2,98; 6,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,06</t>
+          <t>2,65; 6,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,51</t>
+          <t>3,71; 6,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,94</t>
+          <t>2,01; 4,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,87</t>
+          <t>1,8; 3,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,56</t>
+          <t>1,74; 3,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,07</t>
+          <t>1,87; 4,22</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,43</t>
+          <t>1,63; 5,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,19; 1,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,27</t>
+          <t>0,5; 3,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,53</t>
+          <t>2,59; 5,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 9,64</t>
+          <t>4,54; 9,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,59</t>
+          <t>3,95; 8,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,9</t>
+          <t>2,58; 6,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,73</t>
+          <t>5,5; 8,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,09</t>
+          <t>3,65; 6,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,7</t>
+          <t>2,27; 4,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,98</t>
+          <t>1,78; 4,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,57</t>
+          <t>4,28; 6,46</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,23</t>
+          <t>2,19; 7,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,06</t>
+          <t>1,64; 6,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,19</t>
+          <t>0,89; 4,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,18</t>
+          <t>2,04; 5,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,79; 14,38</t>
+          <t>7,97; 14,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,12; 11,31</t>
+          <t>5,33; 11,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,65</t>
+          <t>3,94; 8,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,09</t>
+          <t>1,87; 7,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,77; 9,66</t>
+          <t>5,87; 10,31</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,44</t>
+          <t>4,18; 8,38</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,78</t>
+          <t>2,88; 5,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,44</t>
+          <t>2,09; 5,53</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,1; 13,92</t>
+          <t>4,89; 13,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,87</t>
+          <t>1,31; 7,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,96</t>
+          <t>2,32; 7,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,78</t>
+          <t>2,39; 5,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,68; 10,68</t>
+          <t>4,51; 10,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,17; 16,06</t>
+          <t>9,03; 15,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,81</t>
+          <t>3,9; 9,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,0; 13,12</t>
+          <t>8,98; 13,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,43</t>
+          <t>5,49; 10,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,68; 11,66</t>
+          <t>6,68; 11,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,83</t>
+          <t>4,04; 7,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,52; 9,59</t>
+          <t>6,57; 9,77</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,9</t>
+          <t>1,75; 2,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,8</t>
+          <t>0,96; 1,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,72</t>
+          <t>0,97; 1,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,49</t>
+          <t>1,49; 2,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,06</t>
+          <t>4,58; 6,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,87</t>
+          <t>5,23; 6,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,88</t>
+          <t>3,46; 4,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,07; 5,65</t>
+          <t>4,08; 5,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,31; 4,24</t>
+          <t>3,35; 4,3</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,2</t>
+          <t>3,29; 4,22</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,16</t>
+          <t>2,4; 3,14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,0</t>
+          <t>3,02; 3,97</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>850; 8273</t>
+          <t>843; 7383</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>959; 9169</t>
+          <t>1025; 9767</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4767</t>
+          <t>0; 5660</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 9686</t>
+          <t>0; 8648</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12281; 29743</t>
+          <t>11832; 28775</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3977; 16813</t>
+          <t>4897; 16092</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6682; 19744</t>
+          <t>6472; 19949</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1618; 19004</t>
+          <t>1498; 17141</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14021; 32612</t>
+          <t>13577; 32504</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6967; 20998</t>
+          <t>7819; 21246</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6585; 19841</t>
+          <t>6798; 21297</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2736; 21838</t>
+          <t>2519; 20528</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1922; 11894</t>
+          <t>2648; 11817</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4629; 18213</t>
+          <t>3961; 18181</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1973; 12562</t>
+          <t>1998; 12820</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>166; 8681</t>
+          <t>164; 9687</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20222; 41293</t>
+          <t>19425; 41433</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23315; 47212</t>
+          <t>23187; 47928</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8304; 23264</t>
+          <t>8757; 23228</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6897; 26091</t>
+          <t>6386; 23915</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24069; 48710</t>
+          <t>24095; 46907</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30763; 57965</t>
+          <t>32041; 58795</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13287; 31527</t>
+          <t>13380; 30983</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8961; 26419</t>
+          <t>7884; 26897</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7239; 23382</t>
+          <t>6623; 22990</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1809; 11069</t>
+          <t>1817; 12077</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1071; 10789</t>
+          <t>1052; 9329</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2904; 13961</t>
+          <t>2290; 13748</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14186; 32872</t>
+          <t>14084; 33105</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29203; 54341</t>
+          <t>29521; 55346</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17875; 39248</t>
+          <t>18682; 39640</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8848; 20961</t>
+          <t>9578; 21676</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25255; 49516</t>
+          <t>25635; 49087</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33272; 60483</t>
+          <t>33549; 60478</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20535; 42940</t>
+          <t>20900; 43410</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14374; 30403</t>
+          <t>13899; 30258</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3961; 16920</t>
+          <t>4006; 17327</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1987; 11649</t>
+          <t>2003; 11909</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2192; 13838</t>
+          <t>2428; 14623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5823; 25372</t>
+          <t>4978; 25997</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13595; 32121</t>
+          <t>12767; 31853</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15953; 40708</t>
+          <t>18208; 41990</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17248; 39339</t>
+          <t>17169; 39332</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26211; 46388</t>
+          <t>26439; 46533</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20169; 40745</t>
+          <t>20773; 42223</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22336; 47410</t>
+          <t>22066; 47676</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22459; 46121</t>
+          <t>22479; 44509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30103; 65139</t>
+          <t>29926; 67507</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5701; 20982</t>
+          <t>6287; 21548</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7684</t>
+          <t>817; 8505</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3153; 15615</t>
+          <t>2397; 16435</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14000; 30961</t>
+          <t>14504; 32446</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18803; 38957</t>
+          <t>18322; 39140</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17600; 38469</t>
+          <t>17676; 37909</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12145; 29291</t>
+          <t>12831; 31005</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30116; 47547</t>
+          <t>29983; 48445</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29187; 56062</t>
+          <t>28899; 52736</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20551; 41151</t>
+          <t>19909; 41260</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17431; 38770</t>
+          <t>17382; 39825</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48658; 72590</t>
+          <t>47298; 71368</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6303; 21159</t>
+          <t>6407; 21386</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4889; 18657</t>
+          <t>5058; 19480</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3037; 13994</t>
+          <t>2967; 14225</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7789; 19055</t>
+          <t>7501; 19221</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26712; 49304</t>
+          <t>27338; 48995</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18073; 39927</t>
+          <t>18800; 41084</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14363; 32684</t>
+          <t>14898; 33467</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10671; 43163</t>
+          <t>11381; 42849</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36685; 61414</t>
+          <t>37318; 65550</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27180; 55800</t>
+          <t>27625; 55365</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18877; 41160</t>
+          <t>20536; 42081</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21404; 53113</t>
+          <t>20439; 54048</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10702; 29212</t>
+          <t>10265; 28940</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3312; 19611</t>
+          <t>3255; 18933</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5998; 17877</t>
+          <t>5963; 18583</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6415; 16329</t>
+          <t>6749; 16196</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15635; 35666</t>
+          <t>15062; 36229</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35469; 62112</t>
+          <t>34939; 61542</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16227; 39259</t>
+          <t>15587; 39908</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>38181; 55665</t>
+          <t>38107; 56405</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30894; 56697</t>
+          <t>29861; 55569</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42474; 74103</t>
+          <t>42492; 73653</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25188; 51476</t>
+          <t>26527; 51029</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>46082; 67762</t>
+          <t>46413; 69023</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>58615; 94985</t>
+          <t>57390; 91669</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>34073; 61591</t>
+          <t>32689; 62370</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31640; 58547</t>
+          <t>32914; 58279</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>50926; 86019</t>
+          <t>51668; 87804</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>154147; 204663</t>
+          <t>154672; 206254</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>185300; 243332</t>
+          <t>185266; 243139</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>123591; 172901</t>
+          <t>122626; 175335</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>148904; 206724</t>
+          <t>149245; 208661</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>220429; 281987</t>
+          <t>222735; 286084</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>227342; 292577</t>
+          <t>228931; 294050</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>162858; 218963</t>
+          <t>166431; 217995</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>212144; 284391</t>
+          <t>215097; 282375</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A03-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,49</t>
+          <t>0,17; 1,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,16</t>
+          <t>0,22; 2,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,16</t>
+          <t>2,55; 6,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,75</t>
+          <t>0,96; 3,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,04</t>
+          <t>1,45; 4,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,47</t>
+          <t>0,66; 5,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,38</t>
+          <t>1,48; 3,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,41</t>
+          <t>0,79; 2,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,61</t>
+          <t>0,82; 2,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,88</t>
+          <t>0,44; 3,04</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,61</t>
+          <t>0,26; 1,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,65</t>
+          <t>0,57; 2,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,17</t>
+          <t>0,36; 2,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,29</t>
+          <t>0,33; 3,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,62</t>
+          <t>3,09; 6,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,87</t>
+          <t>3,71; 7,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,12</t>
+          <t>1,48; 4,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,68</t>
+          <t>1,78; 5,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,45</t>
+          <t>1,77; 3,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,54</t>
+          <t>2,34; 4,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,68</t>
+          <t>1,2; 2,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,88</t>
+          <t>1,29; 3,55</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,61</t>
+          <t>1,23; 3,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,78</t>
+          <t>0,26; 1,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,39</t>
+          <t>0,16; 1,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,56</t>
+          <t>0,4; 2,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,8</t>
+          <t>1,99; 4,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 7,84</t>
+          <t>4,07; 7,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,99</t>
+          <t>2,86; 5,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,0</t>
+          <t>1,9; 4,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,7</t>
+          <t>1,9; 3,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,36</t>
+          <t>2,46; 4,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,26</t>
+          <t>1,61; 3,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,8</t>
+          <t>1,29; 2,7</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,34</t>
+          <t>0,74; 3,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,94</t>
+          <t>0,34; 1,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,26</t>
+          <t>0,38; 2,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,93</t>
+          <t>1,37; 4,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,18</t>
+          <t>2,61; 6,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,86</t>
+          <t>2,83; 6,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,06</t>
+          <t>2,59; 5,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,53</t>
+          <t>4,0; 6,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,08</t>
+          <t>1,98; 4,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,89</t>
+          <t>1,71; 3,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,44</t>
+          <t>1,75; 3,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,22</t>
+          <t>2,89; 4,58</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,57</t>
+          <t>1,71; 5,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,99</t>
+          <t>0,19; 1,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,44</t>
+          <t>0,66; 3,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,79</t>
+          <t>2,26; 5,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,69</t>
+          <t>4,78; 9,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,47</t>
+          <t>4,04; 8,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,24</t>
+          <t>2,38; 6,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,89</t>
+          <t>5,35; 8,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 6,67</t>
+          <t>3,64; 7,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,71</t>
+          <t>2,34; 4,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,09</t>
+          <t>1,85; 4,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,46</t>
+          <t>4,29; 6,43</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,31</t>
+          <t>2,37; 7,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,33</t>
+          <t>1,63; 6,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,25</t>
+          <t>0,88; 3,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,22</t>
+          <t>2,08; 5,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,97; 14,29</t>
+          <t>7,86; 14,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,33; 11,64</t>
+          <t>5,26; 11,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,94; 8,86</t>
+          <t>3,69; 8,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,04</t>
+          <t>4,98; 8,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,31</t>
+          <t>5,85; 10,3</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,18; 8,38</t>
+          <t>4,2; 8,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,91</t>
+          <t>2,77; 5,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,53</t>
+          <t>4,02; 6,29</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,89; 13,79</t>
+          <t>4,89; 12,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,6</t>
+          <t>1,34; 7,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 7,23</t>
+          <t>2,29; 6,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,74</t>
+          <t>2,56; 5,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,51; 10,85</t>
+          <t>4,75; 10,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,03; 15,91</t>
+          <t>9,31; 15,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,97</t>
+          <t>4,04; 9,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,98; 13,29</t>
+          <t>8,74; 12,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,22</t>
+          <t>5,54; 10,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,68; 11,58</t>
+          <t>6,5; 11,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,76</t>
+          <t>3,86; 7,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 9,77</t>
+          <t>6,55; 9,6</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,8</t>
+          <t>1,74; 2,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,82</t>
+          <t>0,93; 1,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,72</t>
+          <t>0,94; 1,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,54</t>
+          <t>1,7; 2,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,1</t>
+          <t>4,52; 6,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,86</t>
+          <t>5,22; 6,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,95</t>
+          <t>3,48; 4,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,7</t>
+          <t>4,78; 6,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,35; 4,3</t>
+          <t>3,37; 4,37</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,22</t>
+          <t>3,26; 4,22</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,14</t>
+          <t>2,39; 3,16</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,02; 3,97</t>
+          <t>3,43; 4,24</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>8742</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>10397</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>843; 7383</t>
+          <t>846; 7308</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1025; 9767</t>
+          <t>1007; 9914</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5660</t>
+          <t>0; 4700</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 8648</t>
+          <t>0; 8357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11832; 28775</t>
+          <t>11926; 28973</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4897; 16092</t>
+          <t>4136; 17103</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6472; 19949</t>
+          <t>5735; 19544</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1498; 17141</t>
+          <t>2405; 21692</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13577; 32504</t>
+          <t>14239; 32905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7819; 21246</t>
+          <t>7013; 21102</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6798; 21297</t>
+          <t>6687; 20606</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2519; 20528</t>
+          <t>3401; 23416</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>21355</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2648; 11817</t>
+          <t>1942; 11361</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3961; 18181</t>
+          <t>3884; 19328</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1998; 12820</t>
+          <t>2114; 11992</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>164; 9687</t>
+          <t>1572; 17616</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19425; 41433</t>
+          <t>19305; 40794</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23187; 47928</t>
+          <t>22611; 47434</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8757; 23228</t>
+          <t>8318; 22631</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6386; 23915</t>
+          <t>8927; 26091</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24095; 46907</t>
+          <t>24112; 48054</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32041; 58795</t>
+          <t>30270; 57537</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13380; 30983</t>
+          <t>13874; 31705</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7884; 26897</t>
+          <t>12656; 34734</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14263</t>
+          <t>17241</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>23996</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6623; 22990</t>
+          <t>7842; 24053</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1817; 12077</t>
+          <t>1787; 10923</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1052; 9329</t>
+          <t>1046; 10008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2290; 13748</t>
+          <t>2459; 13769</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14084; 33105</t>
+          <t>13753; 32208</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29521; 55346</t>
+          <t>28732; 55151</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18682; 39640</t>
+          <t>18940; 38642</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9578; 21676</t>
+          <t>11808; 25666</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25635; 49087</t>
+          <t>25181; 49652</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33549; 60478</t>
+          <t>34064; 61894</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20900; 43410</t>
+          <t>21404; 43292</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13899; 30258</t>
+          <t>16025; 33526</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14273</t>
+          <t>15768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>37747</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49970</t>
+          <t>53515</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4006; 17327</t>
+          <t>3851; 17633</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2003; 11909</t>
+          <t>2079; 11586</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2428; 14623</t>
+          <t>2459; 14256</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4978; 25997</t>
+          <t>9598; 28004</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12767; 31853</t>
+          <t>13455; 32782</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18208; 41990</t>
+          <t>17292; 40517</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17169; 39332</t>
+          <t>16811; 38390</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26439; 46533</t>
+          <t>29458; 47945</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20773; 42223</t>
+          <t>20488; 43114</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22066; 47676</t>
+          <t>21035; 46607</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22479; 44509</t>
+          <t>22691; 46813</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29926; 67507</t>
+          <t>41602; 65788</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>21398</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37866</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>59383</t>
+          <t>63861</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6287; 21548</t>
+          <t>6602; 22143</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>817; 8505</t>
+          <t>813; 8066</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2397; 16435</t>
+          <t>3144; 16687</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14504; 32446</t>
+          <t>13724; 30783</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18322; 39140</t>
+          <t>19320; 38446</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17676; 37909</t>
+          <t>18087; 37442</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12831; 31005</t>
+          <t>11845; 29859</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29983; 48445</t>
+          <t>32477; 52062</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28899; 52736</t>
+          <t>28796; 55770</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19909; 41260</t>
+          <t>20511; 43173</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17382; 39825</t>
+          <t>17994; 41260</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>47298; 71368</t>
+          <t>52186; 78161</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>29137</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>38556</t>
+          <t>42629</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6407; 21386</t>
+          <t>6938; 21366</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5058; 19480</t>
+          <t>5018; 19998</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2967; 14225</t>
+          <t>2925; 13022</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7501; 19221</t>
+          <t>8481; 21098</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27338; 48995</t>
+          <t>26966; 48055</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18800; 41084</t>
+          <t>18561; 41073</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14898; 33467</t>
+          <t>13941; 32204</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11381; 42849</t>
+          <t>21873; 37282</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>37318; 65550</t>
+          <t>37193; 65479</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27625; 55365</t>
+          <t>27762; 52838</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20536; 42081</t>
+          <t>19695; 41762</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20439; 54048</t>
+          <t>34022; 53205</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>46637</t>
+          <t>49273</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>57029</t>
+          <t>61422</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10265; 28940</t>
+          <t>10256; 26945</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3255; 18933</t>
+          <t>3331; 19746</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5963; 18583</t>
+          <t>5875; 17278</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6749; 16196</t>
+          <t>7921; 18342</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15062; 36229</t>
+          <t>15854; 36213</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34939; 61542</t>
+          <t>36009; 61755</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15587; 39908</t>
+          <t>16157; 38923</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>38107; 56405</t>
+          <t>40486; 59899</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>29861; 55569</t>
+          <t>30152; 57339</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42492; 73653</t>
+          <t>41319; 71648</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26527; 51029</t>
+          <t>25366; 51427</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>46413; 69023</t>
+          <t>50605; 74168</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68876</t>
+          <t>77041</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>181169</t>
+          <t>200134</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>250045</t>
+          <t>277175</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>57390; 91669</t>
+          <t>56909; 93723</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>32689; 62370</t>
+          <t>31896; 62408</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32914; 58279</t>
+          <t>32060; 56894</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>51668; 87804</t>
+          <t>60192; 93936</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>154672; 206254</t>
+          <t>152853; 207030</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>185266; 243139</t>
+          <t>184917; 244436</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>122626; 175335</t>
+          <t>123306; 171513</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>149245; 208661</t>
+          <t>178432; 226139</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>222735; 286084</t>
+          <t>224272; 290756</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>228931; 294050</t>
+          <t>227027; 293901</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>166431; 217995</t>
+          <t>165567; 219283</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>215097; 282375</t>
+          <t>249208; 307629</t>
         </is>
       </c>
     </row>
